--- a/web/files/港岛-半山区西部-天御第1期.xlsx
+++ b/web/files/港岛-半山区西部-天御第1期.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -8290,7 +8290,7 @@
           <t>- | 4710呎 (3房)
 $35496万
 $75,363/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
@@ -8550,7 +8550,7 @@
           <t>- | 4596呎 (3房)
 $26898万
 $58,526/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -8571,7 +8571,7 @@
           <t>A | 2269呎 (4+房)
 $11288万
 $49,749/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -8579,7 +8579,7 @@
           <t>B | 2281呎 (4+房)
 $11928万
 $52,293/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr"/>
@@ -8598,7 +8598,7 @@
           <t>A | 2269呎 (4+房)
 $10924万
 $48,144/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -8606,7 +8606,7 @@
           <t>B | 2281呎 (4+房)
 $14183万
 $62,180/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr"/>
@@ -8625,7 +8625,7 @@
           <t>A | 2269呎 (4+房)
 $10428万
 $45,960/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -8633,7 +8633,7 @@
           <t>B | 2281呎 (4+房)
 $11222万
 $49,198/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr"/>
@@ -8652,7 +8652,7 @@
           <t>A | 2269呎 (4+房)
 $10820万
 $47,686/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -8660,7 +8660,7 @@
           <t>B | 2281呎 (4+房)
 $10214万
 $44,778/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr"/>
@@ -8679,7 +8679,7 @@
           <t>A | 2269呎 (4+房)
 $9800万
 $43,191/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -8687,7 +8687,7 @@
           <t>B | 2281呎 (4+房)
 $10337万
 $45,318/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr"/>

--- a/web/files/港岛-半山区西部-天御第1期.xlsx
+++ b/web/files/港岛-半山区西部-天御第1期.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,6 +124,12 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -201,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +273,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1734,7 +1743,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1744,12 +1753,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1759,12 +1768,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1774,7 +1783,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8178,27 +8187,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -8525,12 +8534,12 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>- | 4710呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>

--- a/web/files/港岛-半山区西部-天御第1期.xlsx
+++ b/web/files/港岛-半山区西部-天御第1期.xlsx
@@ -1603,7 +1603,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1743,23 +1743,19 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>285709000</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>60660</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1768,12 +1764,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1783,7 +1779,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8193,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8207,7 +8203,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
     </row>
@@ -8494,12 +8490,12 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>- | 4710呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
@@ -8534,12 +8530,12 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>- | 4710呎 (3房)
-招标单位
--
-(在售)</t>
+$28571万
+$60,660/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>
